--- a/Result/profitability/6606.xlsx
+++ b/Result/profitability/6606.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM36"/>
+  <dimension ref="A1:AM37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0.26875</v>
+        <v>0.3175</v>
       </c>
       <c r="N2" t="n">
-        <v>36.345</v>
+        <v>37.49875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.12</v>
       </c>
       <c r="M3" t="n">
-        <v>0.23375</v>
+        <v>0.27875</v>
       </c>
       <c r="N3" t="n">
-        <v>33.8275</v>
+        <v>35.11375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.97</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08875000000000002</v>
+        <v>0.125</v>
       </c>
       <c r="N4" t="n">
-        <v>30.1275</v>
+        <v>30.9375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.55</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0125</v>
+        <v>0.03125</v>
       </c>
       <c r="N5" t="n">
-        <v>27.85</v>
+        <v>28.40125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03250000000000001</v>
+        <v>0.06375000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>25.4975</v>
+        <v>25.725</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.87</v>
       </c>
       <c r="M7" t="n">
-        <v>0.10375</v>
+        <v>0.13125</v>
       </c>
       <c r="N7" t="n">
-        <v>23.26</v>
+        <v>24.1225</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -5000,6 +5000,133 @@
       </c>
       <c r="AM36" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>293</v>
+      </c>
+      <c r="D37" t="n">
+        <v>161</v>
+      </c>
+      <c r="E37" t="n">
+        <v>132</v>
+      </c>
+      <c r="F37" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="G37" t="n">
+        <v>96</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>32.91%</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>100</v>
+      </c>
+      <c r="K37" t="n">
+        <v>61</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="N37" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.115384615384615</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>4.230000000000004</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0.103600293901543</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>4.410000000000004</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.1084870848708488</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK37" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
